--- a/LITERATURE/Literature.xlsx
+++ b/LITERATURE/Literature.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gavin\Documents\GitHub\evac\LITERATURE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379BA40B-9A8C-4443-9D2E-26C679AA734F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E40F001-8AE2-47AD-AAFA-941416EF25CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="Φύλλο1" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Φύλλο1!$A$1:$E$29</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Α/Α</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="91">
   <si>
     <t>Τίτλος</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Keywords</t>
   </si>
   <si>
-    <t>Useful</t>
-  </si>
-  <si>
     <t>Author(s)</t>
   </si>
   <si>
@@ -60,19 +57,351 @@
   </si>
   <si>
     <t>Nawayd M Shaikh, Konstantinos E Kakosimos*, Neil Adia, and Luc Vechot</t>
+  </si>
+  <si>
+    <t>EndNote</t>
+  </si>
+  <si>
+    <t>Influence of Evacuation Policy on Clearance Time under Large-Scale Chemical Accident: AnAgent-Based Modeling</t>
+  </si>
+  <si>
+    <t>Minjun Kim, and Gi-Hyoug Cho</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>A systematic review of methodologies for human behavior modelling and routing optimization in large-scale evacuation planning</t>
+  </si>
+  <si>
+    <t>Razan Y. Aldahlawi, Vahid Akbarib, Glyn Lawson</t>
+  </si>
+  <si>
+    <t>Urban resilience; evacuation model; TRANSIMS; ALOHA;chemical accident; agent-based model</t>
+  </si>
+  <si>
+    <t>Agent-based simulation for pedestrian evacuation: A systematic literature review</t>
+  </si>
+  <si>
+    <t>Pedestrian behaviour modelling, Agent-based modelling, Behavioural decision-making, Emergency evacuation</t>
+  </si>
+  <si>
+    <t>Gayani P.D.P. Senanayake, Minh Kieu, Yang Zou, Kim Dirks</t>
+  </si>
+  <si>
+    <t>Grasping emergency dynamics: A review of group evacuation techniques and strategies in major emergencies</t>
+  </si>
+  <si>
+    <t>Evacuation simulation, Simulation modeling, Strategy optimization, Disaster management, Bibliometric analysis</t>
+  </si>
+  <si>
+    <t>Acute Exposure Guideline Levels (AEGLs) for Time Varying Toxic Plumes</t>
+  </si>
+  <si>
+    <t>J. P. Boris 
+G. Patnaik</t>
+  </si>
+  <si>
+    <t>Toxic airborne contaminants, Health effects prediction, Space and time varying exposures, Extension of EPA AEGLs</t>
+  </si>
+  <si>
+    <t>W.F. ten BERGE, A. ZWART and L.M. APPELMAN</t>
+  </si>
+  <si>
+    <t>Evacuation Decision Model</t>
+  </si>
+  <si>
+    <t>Paul A. Reneke</t>
+  </si>
+  <si>
+    <t>Algorithmic Evaluation of Fire Evacuation Efficiency Under Dynamic Crowd and Smoke Conditions</t>
+  </si>
+  <si>
+    <t>Kim et al., 2026</t>
+  </si>
+  <si>
+    <t>Determining similarity in histological images using graph-theoretic description and matching methods for content-based image retrieval in medical diagnostics</t>
+  </si>
+  <si>
+    <t>Sharma et al., 2012</t>
+  </si>
+  <si>
+    <t>Concentration-time mortality response relationship of irritant and systemically acting vapours and gases</t>
+  </si>
+  <si>
+    <t>A Systematic Literature Review of A* Pathfinding</t>
+  </si>
+  <si>
+    <t>Daniel Foead, Alifio Ghifari, Marchel Budi Kusuma, Novita Hanafiah, Eric Gunawan</t>
+  </si>
+  <si>
+    <t>Sharmad Rajnish Lawande, Graceline Jasmine, Jani Anbarasi and LilaIznita Izhar</t>
+  </si>
+  <si>
+    <t>A Systematic Review and Analysis of Intelligence-Based Pathfinding Algorithms in the Field of Video Games</t>
+  </si>
+  <si>
+    <t>An evacuation path planning method for multi-hazard accidents in chemical industries based on risk perception</t>
+  </si>
+  <si>
+    <t>Zhichao He, Kaixin Shen, Meng Lan, Wenguo Weng</t>
+  </si>
+  <si>
+    <t>Application of Dijkstra's Algorithm to Determine the Shortest Route from City Center to Medan City Tourist Attractions</t>
+  </si>
+  <si>
+    <t>Liskedame Yanti Sipayung, Chaston Ramotto Sinaga, Angelica Claudia Sagala</t>
+  </si>
+  <si>
+    <t>Dijkstra's algorithm, shortest route</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence - A Modern Approach</t>
+  </si>
+  <si>
+    <t>Stuart Russell and Peter Norvig</t>
+  </si>
+  <si>
+    <t>Comparison of Pathfinding Algorithms in Dynamic and Congested Environments</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>BIRUK DEBEBE KEBEDE, JACOB FRIEDRICH</t>
+  </si>
+  <si>
+    <t>D* Lite</t>
+  </si>
+  <si>
+    <t>Sven Koenig, Maxim Likhachev</t>
+  </si>
+  <si>
+    <t>Julia: A Fast Dynamic Language for Technical Computing</t>
+  </si>
+  <si>
+    <t>Jeff Bezanson, Stefan Karpinski, Viral B. Shah, Alan Edelman</t>
+  </si>
+  <si>
+    <t>Deep Neural Network-based Optimization Framework for Safety Evacuation Route during Toxic Gas Leak Incidents</t>
+  </si>
+  <si>
+    <t>Seung-Kwon Seo, Young-Gak Yoon, Ju-sung Lee, Jonggeol Na, Chul-Jin Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evacuation; Toxic gas leak; Computational fluid dynamics; Surrogate model; Variational autoencoder </t>
+  </si>
+  <si>
+    <t>Harshita Sharma, Alexander Alekseychuk, Peter Leskovsky, Olaf Hellwich, RS Anand, Norman Zerbe and Peter Hufnagl</t>
+  </si>
+  <si>
+    <t>Developing and validating evacuation models for fire safety engineering</t>
+  </si>
+  <si>
+    <t>Enrico Ronchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evacuation; Egress; Human behaviour; Modelling; Simulation; Fire safety </t>
+  </si>
+  <si>
+    <t>Dynamic crowd evacuation approach for the emergency route planning problem: Application to case studies</t>
+  </si>
+  <si>
+    <t>Mohd Nor Akmal Khalid, Umi Kalsom Yusof</t>
+  </si>
+  <si>
+    <t>Emergency evacuation; Emergency route planning problem; Dynamic crowd evacuation; Artificial immune system</t>
+  </si>
+  <si>
+    <t>Dynamic evacuation path planning for subway station fire based on IACO</t>
+  </si>
+  <si>
+    <t>Zhaohui Liu, Ruihong Zou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subway fire; Ant colony; FDS simulation; Evacuation path </t>
+  </si>
+  <si>
+    <t>Dynamic path planning for autonomous driving on various roads with avoidance of static and moving obstacles</t>
+  </si>
+  <si>
+    <t>Xuemin Hu, Long Chen, Bo Tang, Dongpu Cao, Haibo He</t>
+  </si>
+  <si>
+    <t>Path planning; Path generation; Path selection; Obstacle avoidance; Autonomous driving</t>
+  </si>
+  <si>
+    <t>Dynamic Routing during Disaster Events</t>
+  </si>
+  <si>
+    <t>Siska Fitrianie, Leon J. M. Rothkrantz</t>
+  </si>
+  <si>
+    <t>Evacuation, disaster events, dynamic routing, mitigation planning</t>
+  </si>
+  <si>
+    <t>The D* Algorithm for Real-Time Planning of Optimal Traverses</t>
+  </si>
+  <si>
+    <t>Anthony Stentz</t>
+  </si>
+  <si>
+    <t>Online Indoor Fire Evacuation System</t>
+  </si>
+  <si>
+    <t>An-Fong Lee and Pei-Hsuan Tsai</t>
+  </si>
+  <si>
+    <t>Real-time evacuation route optimization in the fire scenarios of cruise ships</t>
+  </si>
+  <si>
+    <t>Linfan Liu, Huajun Zhang, Jun Shi, Jianning Geng</t>
+  </si>
+  <si>
+    <t>Cruise ship; Dijkstra algorithm; Evacuees; Fire simulation</t>
+  </si>
+  <si>
+    <t>Social force model for pedestrian dynamics</t>
+  </si>
+  <si>
+    <t>Dirk Helbing and Peter Molnar</t>
+  </si>
+  <si>
+    <t>Disaster; Large-scale emergency; Human factors; Optimization; Evacuation planning; Evacuation behavior; Routing problems</t>
+  </si>
+  <si>
+    <r>
+      <t>Hai Sun</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="161"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Guorui Han</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="161"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Xiaowei Zhang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="161"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Xuejing Ruan</t>
+    </r>
+  </si>
+  <si>
+    <t>Hyunseok Kim, Sunnie Haam, Mintaek Yoo and Woo Seung Song</t>
+  </si>
+  <si>
+    <t>AStar, Pathfinding, Heuristic function, HPA-STAR</t>
+  </si>
+  <si>
+    <t>pathfinding; Breadth First Search; AStar; Dijkstra’s; Greedy Best First; Unity</t>
+  </si>
+  <si>
+    <t>fire evacuation; dynamic crowd; smoke propagation; Dijkstra algorithm; AStar algorithm; evacuation efficiency; predictive control system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency evacuation; Multi-hazard accident; Risk analysis; Chemical industry; DStar algorithm </t>
+  </si>
+  <si>
+    <t>Pathfinding, global pathfinding, local pathfinding, incremental search, LPAStar (Long life planning), DStar Lite, static environment, dynamic environment, heuristic</t>
+  </si>
+  <si>
+    <t>Attributed Relational Graphs (ARG), Region of Interest (ROI), Breast tissue biopsy, Connected components, Graph-theoretic, AStar search</t>
+  </si>
+  <si>
+    <t>DStar Lite, indoor fire evacuation, navigation, path planning</t>
+  </si>
+  <si>
+    <t>Determination of emergency assembly point for industrial accidents with AHP analysis</t>
+  </si>
+  <si>
+    <t>Onur Hoscan, Saliha Cetinyokus</t>
+  </si>
+  <si>
+    <t>Industrial accidents; Emergency plans; Emergency assembly point; Multi-criteria decision making; AHP</t>
+  </si>
+  <si>
+    <t>Poison Center Surveillance of Occupational Incidents with Hazardous Materials (2016–2023): Insights for Risk Mitigation and Incident Preparedness</t>
+  </si>
+  <si>
+    <t>Anja P. G. Wijnands, Arjen Koppen, Irma de Vries, Dylan W. de Lange and Saskia J. Rietjens</t>
+  </si>
+  <si>
+    <t>HAZMAT incidents; chemical incidents; surveillance; public health risks; poison information centers; prevention; risk mitigation strategies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="161"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,19 +424,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,14 +756,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BBD8B3-F96C-463C-A119-D4DE198D4556}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.59765625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="71" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" style="3"/>
-    <col min="5" max="5" width="63.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="97.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.09765625" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.796875" style="3"/>
   </cols>
   <sheetData>
@@ -438,49 +771,449 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="6">
+        <v>2020</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="6">
+        <v>2022</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="6">
+        <v>2014</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2023</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2022</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1986</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2002</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2022</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2021</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2012</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2021</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2018</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2024</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2018</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2015</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2013</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
+      <c r="B25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2020</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2012</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2023</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2025</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="6">
+        <v>2023</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1995</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1994</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E29" xr:uid="{F5BBD8B3-F96C-463C-A119-D4DE198D4556}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+      <sortCondition ref="A1:A29"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LITERATURE/Literature.xlsx
+++ b/LITERATURE/Literature.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gavin\Documents\GitHub\evac\LITERATURE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E40F001-8AE2-47AD-AAFA-941416EF25CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D358CD3-7E3F-4B9B-A359-B95CC4805557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="94">
   <si>
     <t>Τίτλος</t>
   </si>
@@ -376,12 +376,21 @@
   <si>
     <t>HAZMAT incidents; chemical incidents; surveillance; public health risks; poison information centers; prevention; risk mitigation strategies</t>
   </si>
+  <si>
+    <t>Characteristics and Statistical Analysis of Large and above Hazardous Chemical Accidents in China from 2000 to 2020</t>
+  </si>
+  <si>
+    <t>Yu Zheng, Kai Peng, Lidong Pan, Juan Zheng, Baojing Xie and Bohong Wang</t>
+  </si>
+  <si>
+    <t>chemical safety; hazardous chemical; the entropy weight method; TOPSIS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -401,6 +410,13 @@
       <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF172B4D"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="161"/>
     </font>
   </fonts>
@@ -424,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -441,6 +457,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5BBD8B3-F96C-463C-A119-D4DE198D4556}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="97.09765625" style="2" bestFit="1" customWidth="1"/>
@@ -913,303 +932,335 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="54" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2022</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="54" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C12" s="6">
         <v>2025</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C13" s="6">
         <v>1986</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C15" s="6">
         <v>2002</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C16" s="6">
         <v>2022</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+    <row r="17" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C17" s="6">
         <v>2021</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C18" s="6">
         <v>2012</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C19" s="6">
         <v>2021</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+    <row r="20" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C20" s="6">
         <v>2018</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C21" s="6">
         <v>2024</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+    <row r="22" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C22" s="6">
         <v>2018</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C23" s="6">
         <v>2015</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C24" s="6">
         <v>2013</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C25" s="6">
         <v>2025</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="36" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="26" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C26" s="6">
         <v>2020</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C27" s="6">
         <v>2012</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C28" s="6">
         <v>2023</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:5" ht="36" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C29" s="6">
         <v>2025</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="6">
-        <v>2023</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>41</v>
+        <v>70</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="C30" s="6">
-        <v>1995</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>74</v>
+        <v>2023</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C31" s="6">
+        <v>1995</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="6">
         <v>1994</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>67</v>
       </c>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="7"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="7"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E29" xr:uid="{F5BBD8B3-F96C-463C-A119-D4DE198D4556}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E32">
       <sortCondition ref="A1:A29"/>
     </sortState>
   </autoFilter>
